--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260309_202414.xlsx
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
